--- a/excel_project/部门考勤数据/海运部 (Ocean Freight)_异常考勤数据.xlsx
+++ b/excel_project/部门考勤数据/海运部 (Ocean Freight)_异常考勤数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>陈管香-Vera Chen</t>
+          <t>陈雪华- Sylvia Chen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,23 +478,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25-10-17 星期五</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
+          <t>25-11-19 星期三</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>缺卡</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -511,23 +511,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25-09-22 星期一</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>25-10-20 星期一</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>缺卡</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>22:53</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>正常</t>
         </is>
       </c>
     </row>
@@ -544,17 +544,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25-09-23 星期二</t>
+          <t>25-10-21 星期二</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>迟到</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -577,27 +577,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25-09-24 星期三</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
+          <t>25-10-23 星期四</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>迟到</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>21:21</t>
-        </is>
-      </c>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缺卡</t>
         </is>
       </c>
     </row>
@@ -614,23 +606,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25-09-25 星期四</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>25-10-27 星期一</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>缺卡</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>21:58</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>正常</t>
         </is>
       </c>
     </row>
@@ -647,19 +639,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25-09-26 星期五</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>25-10-29 星期三</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>缺卡</t>
+          <t>迟到</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>管理员莫良-Peter Mo改为正常</t>
+          <t>缺卡</t>
         </is>
       </c>
     </row>
@@ -676,12 +672,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25-10-10 星期五</t>
+          <t>25-10-30 星期四</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -691,7 +687,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23:46</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -713,12 +709,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25-10-11 星期六</t>
+          <t>25-10-31 星期五</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -728,7 +724,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -750,12 +746,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25-10-13 星期一</t>
+          <t>25-11-04 星期二</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -765,7 +761,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -787,23 +783,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25-10-15 星期三</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>25-11-05 星期三</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>缺卡</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>20:04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>正常</t>
         </is>
       </c>
     </row>
@@ -820,23 +816,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25-10-17 星期五</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
+          <t>25-11-06 星期四</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>迟到</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>缺卡</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -853,17 +849,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25-10-20 星期一</t>
+          <t>25-11-12 星期三</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -876,7 +872,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>李玥婷-Cherry Li</t>
+          <t>韩璐-Amanda Han</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -886,34 +882,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>25-09-22 星期一</t>
+          <t>25-11-17 星期一</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>迟到</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>李玥婷-Cherry Li</t>
+          <t>韩璐-Amanda Han</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -923,34 +919,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>25-10-17 星期五</t>
+          <t>25-11-18 星期二</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>迟到</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>刘佳敏-Ada Liu</t>
+          <t>韩璐-Amanda Han</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -960,64 +956,455 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25-09-28 星期日</t>
+          <t>25-11-19 星期三</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>迟到</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>韩璐-Amanda Han</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25-11-20 星期四</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>未打卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>李玥婷-Cherry Li</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>25-10-23 星期四</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>李玥婷-Cherry Li</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>25-11-10 星期一</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>刘佳敏-Ada Liu</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>25-10-21 星期二</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>刘佳敏-Ada Liu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>25-10-29 星期三</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>刘佳敏-Ada Liu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25-10-31 星期五</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>刘佳敏-Ada Liu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>25-11-12 星期三</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>杨蓓琴-Anya Yang</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>海运部 (Ocean Freight)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>25-10-16 星期四</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>25-10-30 星期四</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>补卡审批通过</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>杨蓓琴-Anya Yang</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>25-10-31 星期五</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>杨蓓琴-Anya Yang</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>25-11-04 星期二</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>杨蓓琴-Anya Yang</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>25-11-18 星期二</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>赵爽-Luna Zhao</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>海运部 (Ocean Freight)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>25-11-03 星期一</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>早退</t>
         </is>
       </c>
     </row>
